--- a/output/roomself_excel/1852.xlsx
+++ b/output/roomself_excel/1852.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>524026</v>
+        <v>144573</v>
       </c>
       <c r="D2" t="n">
-        <v>7040</v>
+        <v>3064</v>
       </c>
       <c r="E2" t="n">
-        <v>1287</v>
+        <v>495</v>
       </c>
       <c r="F2" t="n">
-        <v>723</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3618</v>
+        <v>524026</v>
       </c>
       <c r="D3" t="n">
-        <v>644</v>
+        <v>7040</v>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1287</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>723</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>102437</v>
+        <v>142127</v>
       </c>
       <c r="D5" t="n">
-        <v>4248</v>
+        <v>3072</v>
       </c>
       <c r="E5" t="n">
-        <v>899</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>62964</v>
+        <v>120234</v>
       </c>
       <c r="D6" t="n">
-        <v>2036</v>
+        <v>3120</v>
       </c>
       <c r="E6" t="n">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="F6" t="n">
-        <v>261</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -576,14 +576,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5429</v>
+        <v>24180</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>1244</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5185</v>
+        <v>14161</v>
       </c>
       <c r="D8" t="n">
-        <v>584</v>
+        <v>952</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -620,14 +620,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5002</v>
+        <v>11948</v>
       </c>
       <c r="D9" t="n">
-        <v>572</v>
+        <v>876</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4819</v>
+        <v>83210</v>
       </c>
       <c r="D10" t="n">
-        <v>560</v>
+        <v>2580</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5490</v>
+        <v>21894</v>
       </c>
       <c r="D11" t="n">
-        <v>604</v>
+        <v>1204</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4819</v>
+        <v>272067</v>
       </c>
       <c r="D12" t="n">
-        <v>560</v>
+        <v>8323</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>272067</v>
+        <v>36417</v>
       </c>
       <c r="D13" t="n">
-        <v>8323</v>
+        <v>1528</v>
       </c>
       <c r="E13" t="n">
-        <v>494</v>
+        <v>163</v>
       </c>
       <c r="F13" t="n">
-        <v>438</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>142127</v>
+        <v>13068</v>
       </c>
       <c r="D14" t="n">
-        <v>3072</v>
+        <v>924</v>
       </c>
       <c r="E14" t="n">
-        <v>270</v>
+        <v>132</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36417</v>
+        <v>3647</v>
       </c>
       <c r="D15" t="n">
-        <v>1528</v>
+        <v>930</v>
       </c>
       <c r="E15" t="n">
-        <v>645</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5148</v>
+        <v>65800</v>
       </c>
       <c r="D16" t="n">
-        <v>604</v>
+        <v>2152</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,17 +796,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13068</v>
+        <v>14399</v>
       </c>
       <c r="D17" t="n">
-        <v>924</v>
+        <v>960</v>
       </c>
       <c r="E17" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F17" t="n">
         <v>49</v>
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>120234</v>
+        <v>218160</v>
       </c>
       <c r="D18" t="n">
-        <v>3120</v>
+        <v>4092</v>
       </c>
       <c r="E18" t="n">
-        <v>334</v>
+        <v>859</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3647</v>
+        <v>29172</v>
       </c>
       <c r="D19" t="n">
-        <v>930</v>
+        <v>1372</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>137330</v>
+        <v>20234</v>
       </c>
       <c r="D20" t="n">
-        <v>3012</v>
+        <v>1140</v>
       </c>
       <c r="E20" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>205414</v>
+        <v>163800</v>
       </c>
       <c r="D21" t="n">
-        <v>5713</v>
+        <v>3348</v>
       </c>
       <c r="E21" t="n">
-        <v>458</v>
+        <v>312</v>
       </c>
       <c r="F21" t="n">
-        <v>301</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4708</v>
+        <v>20952</v>
       </c>
       <c r="D22" t="n">
-        <v>949</v>
+        <v>1252</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21894</v>
+        <v>3618</v>
       </c>
       <c r="D23" t="n">
-        <v>1204</v>
+        <v>644</v>
       </c>
       <c r="E23" t="n">
-        <v>342</v>
+        <v>185</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>102437</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>4248</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>899</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>144573</v>
+        <v>62964</v>
       </c>
       <c r="D25" t="n">
-        <v>3064</v>
+        <v>2036</v>
       </c>
       <c r="E25" t="n">
-        <v>495</v>
+        <v>346</v>
       </c>
       <c r="F25" t="n">
-        <v>386</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26">
@@ -994,14 +994,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24180</v>
+        <v>5429</v>
       </c>
       <c r="D26" t="n">
-        <v>1244</v>
+        <v>600</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>60444</v>
+        <v>5185</v>
       </c>
       <c r="D27" t="n">
-        <v>2304</v>
+        <v>584</v>
       </c>
       <c r="E27" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14161</v>
+        <v>5002</v>
       </c>
       <c r="D28" t="n">
-        <v>952</v>
+        <v>572</v>
       </c>
       <c r="E28" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14399</v>
+        <v>4819</v>
       </c>
       <c r="D29" t="n">
-        <v>960</v>
+        <v>560</v>
       </c>
       <c r="E29" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37018</v>
+        <v>5490</v>
       </c>
       <c r="D30" t="n">
-        <v>2116</v>
+        <v>604</v>
       </c>
       <c r="E30" t="n">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1104,20 +1104,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>218160</v>
+        <v>4819</v>
       </c>
       <c r="D31" t="n">
-        <v>4092</v>
+        <v>560</v>
       </c>
       <c r="E31" t="n">
-        <v>859</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15980</v>
+        <v>5148</v>
       </c>
       <c r="D32" t="n">
-        <v>1212</v>
+        <v>604</v>
       </c>
       <c r="E32" t="n">
-        <v>269</v>
+        <v>52</v>
       </c>
       <c r="F32" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>263562</v>
+        <v>137330</v>
       </c>
       <c r="D33" t="n">
-        <v>4228</v>
+        <v>3012</v>
       </c>
       <c r="E33" t="n">
-        <v>699</v>
+        <v>492</v>
       </c>
       <c r="F33" t="n">
-        <v>496</v>
+        <v>359</v>
       </c>
     </row>
     <row r="34">
@@ -1170,20 +1170,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29172</v>
+        <v>205414</v>
       </c>
       <c r="D34" t="n">
-        <v>1372</v>
+        <v>5713</v>
       </c>
       <c r="E34" t="n">
-        <v>160</v>
+        <v>326</v>
       </c>
       <c r="F34" t="n">
-        <v>156</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35">
@@ -1192,14 +1192,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>65800</v>
+        <v>4708</v>
       </c>
       <c r="D35" t="n">
-        <v>2152</v>
+        <v>949</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>133700</v>
+        <v>21894</v>
       </c>
       <c r="D36" t="n">
-        <v>2928</v>
+        <v>1204</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>139762</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3068</v>
+        <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>21708</v>
+        <v>60444</v>
       </c>
       <c r="D38" t="n">
-        <v>1184</v>
+        <v>2304</v>
       </c>
       <c r="E38" t="n">
-        <v>234</v>
+        <v>462</v>
       </c>
       <c r="F38" t="n">
-        <v>134</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39">
@@ -1280,20 +1280,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>20234</v>
+        <v>37018</v>
       </c>
       <c r="D39" t="n">
-        <v>1140</v>
+        <v>2116</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40">
@@ -1306,16 +1306,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16884</v>
+        <v>15980</v>
       </c>
       <c r="D40" t="n">
-        <v>1040</v>
+        <v>1212</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
@@ -1324,20 +1324,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>163800</v>
+        <v>263562</v>
       </c>
       <c r="D41" t="n">
-        <v>3348</v>
+        <v>4228</v>
       </c>
       <c r="E41" t="n">
-        <v>498</v>
+        <v>699</v>
       </c>
       <c r="F41" t="n">
-        <v>392</v>
+        <v>496</v>
       </c>
     </row>
     <row r="42">
@@ -1350,16 +1350,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>161708</v>
+        <v>133700</v>
       </c>
       <c r="D42" t="n">
-        <v>5027</v>
+        <v>2928</v>
       </c>
       <c r="E42" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1368,20 +1368,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11948</v>
+        <v>139762</v>
       </c>
       <c r="D43" t="n">
-        <v>876</v>
+        <v>3068</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
@@ -1390,20 +1390,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>83210</v>
+        <v>21708</v>
       </c>
       <c r="D44" t="n">
-        <v>2580</v>
+        <v>1184</v>
       </c>
       <c r="E44" t="n">
-        <v>379</v>
+        <v>102</v>
       </c>
       <c r="F44" t="n">
-        <v>237</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44596</v>
+        <v>16884</v>
       </c>
       <c r="D45" t="n">
-        <v>1812</v>
+        <v>1040</v>
       </c>
       <c r="E45" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1438,16 +1438,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>41082</v>
+        <v>140542</v>
       </c>
       <c r="D46" t="n">
-        <v>1828</v>
+        <v>4159</v>
       </c>
       <c r="E46" t="n">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="F46" t="n">
-        <v>173</v>
+        <v>278</v>
       </c>
     </row>
     <row r="47">
@@ -1456,20 +1456,64 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>21894</v>
+        <v>214</v>
       </c>
       <c r="D47" t="n">
-        <v>1204</v>
+        <v>648</v>
       </c>
       <c r="E47" t="n">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>44596</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1812</v>
+      </c>
+      <c r="E48" t="n">
+        <v>241</v>
+      </c>
+      <c r="F48" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>41082</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E49" t="n">
+        <v>379</v>
+      </c>
+      <c r="F49" t="n">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1852.xlsx
+++ b/output/roomself_excel/1852.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>3064</v>
       </c>
-      <c r="E2" t="n">
-        <v>495</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>386</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>429</v>
+      </c>
+      <c r="J2" t="n">
+        <v>49</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>7040</v>
       </c>
-      <c r="E3" t="n">
-        <v>1287</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>723</v>
-      </c>
+        <v>1342</v>
+      </c>
+      <c r="G3" t="n">
+        <v>49</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>492</v>
+      </c>
+      <c r="J3" t="n">
+        <v>49</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,31 @@
       <c r="D4" t="n">
         <v>3148</v>
       </c>
-      <c r="E4" t="n">
-        <v>495</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>390</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="G4" t="n">
+        <v>49</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>341</v>
+      </c>
+      <c r="J4" t="n">
+        <v>49</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,23 @@
       <c r="D5" t="n">
         <v>3072</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="G5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,23 @@
       <c r="D6" t="n">
         <v>3120</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>334</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>49</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +699,15 @@
       <c r="D7" t="n">
         <v>1244</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,23 @@
       <c r="D8" t="n">
         <v>952</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>119</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>49</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +757,15 @@
       <c r="D9" t="n">
         <v>876</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +782,31 @@
       <c r="D10" t="n">
         <v>2580</v>
       </c>
-      <c r="E10" t="n">
-        <v>379</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>236</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="G10" t="n">
+        <v>33</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>191</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +823,23 @@
       <c r="D11" t="n">
         <v>1204</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>178</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>50</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +856,23 @@
       <c r="D12" t="n">
         <v>8323</v>
       </c>
-      <c r="E12" t="n">
-        <v>494</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>438</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="G12" t="n">
+        <v>49</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +889,15 @@
       <c r="D13" t="n">
         <v>1528</v>
       </c>
-      <c r="E13" t="n">
-        <v>163</v>
-      </c>
-      <c r="F13" t="n">
-        <v>15</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +914,23 @@
       <c r="D14" t="n">
         <v>924</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>132</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>49</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +947,15 @@
       <c r="D15" t="n">
         <v>930</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +972,15 @@
       <c r="D16" t="n">
         <v>2152</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +997,23 @@
       <c r="D17" t="n">
         <v>960</v>
       </c>
-      <c r="E17" t="n">
-        <v>121</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
+        <v>116</v>
+      </c>
+      <c r="G17" t="n">
         <v>49</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,11 +1030,38 @@
       <c r="D18" t="n">
         <v>4092</v>
       </c>
-      <c r="E18" t="n">
-        <v>859</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>336</v>
+        <v>720</v>
+      </c>
+      <c r="G18" t="n">
+        <v>33</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>79</v>
+      </c>
+      <c r="J18" t="n">
+        <v>25</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>34</v>
+      </c>
+      <c r="M18" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -849,12 +1079,23 @@
       <c r="D19" t="n">
         <v>1372</v>
       </c>
-      <c r="E19" t="n">
-        <v>160</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>156</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="G19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1112,15 @@
       <c r="D20" t="n">
         <v>1140</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1137,23 @@
       <c r="D21" t="n">
         <v>3348</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>312</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>45</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1170,23 @@
       <c r="D22" t="n">
         <v>1252</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>97</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>50</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1203,23 @@
       <c r="D23" t="n">
         <v>644</v>
       </c>
-      <c r="E23" t="n">
-        <v>185</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1236,31 @@
       <c r="D24" t="n">
         <v>4248</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>899</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>49</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>163</v>
+      </c>
+      <c r="J24" t="n">
+        <v>48</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1277,31 @@
       <c r="D25" t="n">
         <v>2036</v>
       </c>
-      <c r="E25" t="n">
-        <v>346</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>261</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="G25" t="n">
+        <v>49</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>212</v>
+      </c>
+      <c r="J25" t="n">
+        <v>49</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1318,15 @@
       <c r="D26" t="n">
         <v>600</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1343,15 @@
       <c r="D27" t="n">
         <v>584</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1368,15 @@
       <c r="D28" t="n">
         <v>572</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1393,15 @@
       <c r="D29" t="n">
         <v>560</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1418,15 @@
       <c r="D30" t="n">
         <v>604</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1443,15 @@
       <c r="D31" t="n">
         <v>560</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1468,15 @@
       <c r="D32" t="n">
         <v>604</v>
       </c>
-      <c r="E32" t="n">
-        <v>52</v>
-      </c>
-      <c r="F32" t="n">
-        <v>49</v>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1493,31 @@
       <c r="D33" t="n">
         <v>3012</v>
       </c>
-      <c r="E33" t="n">
-        <v>492</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F33" t="n">
-        <v>359</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="G33" t="n">
+        <v>49</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>310</v>
+      </c>
+      <c r="J33" t="n">
+        <v>49</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1179,12 +1534,23 @@
       <c r="D34" t="n">
         <v>5713</v>
       </c>
-      <c r="E34" t="n">
-        <v>326</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>301</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="G34" t="n">
+        <v>49</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1201,12 +1567,15 @@
       <c r="D35" t="n">
         <v>949</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1223,12 +1592,23 @@
       <c r="D36" t="n">
         <v>1204</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>141</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>13</v>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1245,12 +1625,15 @@
       <c r="D37" t="n">
         <v>12</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1267,12 +1650,31 @@
       <c r="D38" t="n">
         <v>2304</v>
       </c>
-      <c r="E38" t="n">
-        <v>462</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>187</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="G38" t="n">
+        <v>48</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>438</v>
+      </c>
+      <c r="J38" t="n">
+        <v>49</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1289,12 +1691,31 @@
       <c r="D39" t="n">
         <v>2116</v>
       </c>
-      <c r="E39" t="n">
-        <v>495</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>132</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="G39" t="n">
+        <v>49</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>446</v>
+      </c>
+      <c r="J39" t="n">
+        <v>49</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1311,11 +1732,38 @@
       <c r="D40" t="n">
         <v>1212</v>
       </c>
-      <c r="E40" t="n">
-        <v>269</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>81</v>
+        <v>68</v>
+      </c>
+      <c r="G40" t="n">
+        <v>13</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>235</v>
+      </c>
+      <c r="J40" t="n">
+        <v>13</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>68</v>
+      </c>
+      <c r="M40" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="41">
@@ -1333,11 +1781,38 @@
       <c r="D41" t="n">
         <v>4228</v>
       </c>
-      <c r="E41" t="n">
-        <v>699</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F41" t="n">
-        <v>496</v>
+        <v>654</v>
+      </c>
+      <c r="G41" t="n">
+        <v>48</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>403</v>
+      </c>
+      <c r="J41" t="n">
+        <v>45</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>144</v>
+      </c>
+      <c r="M41" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -1355,12 +1830,15 @@
       <c r="D42" t="n">
         <v>2928</v>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1377,12 +1855,23 @@
       <c r="D43" t="n">
         <v>3068</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>469</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>33</v>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1399,12 +1888,23 @@
       <c r="D44" t="n">
         <v>1184</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>102</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>45</v>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1421,12 +1921,15 @@
       <c r="D45" t="n">
         <v>1040</v>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1443,12 +1946,31 @@
       <c r="D46" t="n">
         <v>4159</v>
       </c>
-      <c r="E46" t="n">
-        <v>371</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F46" t="n">
-        <v>278</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="G46" t="n">
+        <v>18</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>260</v>
+      </c>
+      <c r="J46" t="n">
+        <v>50</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1465,12 +1987,15 @@
       <c r="D47" t="n">
         <v>648</v>
       </c>
-      <c r="E47" t="n">
-        <v>50</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1487,12 +2012,23 @@
       <c r="D48" t="n">
         <v>1812</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
         <v>241</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>50</v>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1509,12 +2045,31 @@
       <c r="D49" t="n">
         <v>1828</v>
       </c>
-      <c r="E49" t="n">
-        <v>379</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F49" t="n">
-        <v>173</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="G49" t="n">
+        <v>45</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>334</v>
+      </c>
+      <c r="J49" t="n">
+        <v>50</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/1852.xlsx
+++ b/output/roomself_excel/1852.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,66 @@
           <t>ExtWallWidth_3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -535,6 +595,42 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>49</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>152</v>
+      </c>
+      <c r="U2" t="n">
+        <v>49</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -576,6 +672,42 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>563</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>49</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>222</v>
+      </c>
+      <c r="U3" t="n">
+        <v>49</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -617,6 +749,30 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>49</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -650,6 +806,30 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>48</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -683,6 +863,30 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>49</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -708,6 +912,18 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -741,6 +957,18 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -766,6 +994,18 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -807,6 +1047,30 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -840,6 +1104,18 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -873,6 +1149,42 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>49</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>116</v>
+      </c>
+      <c r="U12" t="n">
+        <v>49</v>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -898,6 +1210,18 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -931,6 +1255,30 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>49</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -956,6 +1304,18 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -981,6 +1341,18 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1014,6 +1386,30 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>49</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1063,6 +1459,18 @@
       <c r="M18" t="n">
         <v>33</v>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1096,6 +1504,18 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1121,6 +1541,18 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1154,6 +1586,30 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>45</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1187,6 +1643,18 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1220,6 +1688,30 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>11</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1261,6 +1753,30 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>49</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1302,6 +1818,30 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>49</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1327,6 +1867,18 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1352,6 +1904,18 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1377,6 +1941,18 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1402,6 +1978,18 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1427,6 +2015,18 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1452,6 +2052,18 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1477,6 +2089,18 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1518,6 +2142,42 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>49</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>179</v>
+      </c>
+      <c r="U33" t="n">
+        <v>49</v>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1551,6 +2211,42 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>49</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>61</v>
+      </c>
+      <c r="U34" t="n">
+        <v>49</v>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1576,6 +2272,18 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1609,6 +2317,18 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1634,6 +2354,18 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1675,6 +2407,18 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1716,6 +2460,18 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1765,6 +2521,18 @@
       <c r="M40" t="n">
         <v>21</v>
       </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1812,6 +2580,54 @@
         <v>144</v>
       </c>
       <c r="M41" t="n">
+        <v>45</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>48</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>241</v>
+      </c>
+      <c r="U41" t="n">
+        <v>45</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y41" t="n">
         <v>45</v>
       </c>
     </row>
@@ -1839,6 +2655,18 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1872,6 +2700,30 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>33</v>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1905,6 +2757,18 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1930,6 +2794,18 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1971,6 +2847,18 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1996,6 +2884,18 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2029,6 +2929,30 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>50</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2070,6 +2994,18 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
